--- a/src/uploads/账号库模板.xlsx
+++ b/src/uploads/账号库模板.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfpp2012/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfpp2012/codes/task-backend/src/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FA3E994-F0DE-4B46-901E-C7D2BD95125E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F356F30A-D206-F448-9A59-0E8580766722}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8260" yWindow="5840" windowWidth="28040" windowHeight="17440" xr2:uid="{DA612C98-B207-AA43-B9D3-B2B5CC3324FF}"/>
+    <workbookView xWindow="8260" yWindow="3220" windowWidth="28040" windowHeight="17440" xr2:uid="{DA612C98-B207-AA43-B9D3-B2B5CC3324FF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,19 +33,19 @@
     <t>平台</t>
   </si>
   <si>
-    <t>账号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	窗口序号</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	平台账号</t>
-  </si>
-  <si>
     <t>河内</t>
   </si>
   <si>
     <t>Shopee</t>
+  </si>
+  <si>
+    <t>下单账号序号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	登录账号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	登录密码</t>
   </si>
 </sst>
 </file>
@@ -399,6 +399,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA12DFE6-C76C-454B-8EC9-D3CF9DB0B43E}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="16.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="27" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
@@ -408,21 +415,21 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2">
         <v>111</v>

--- a/src/uploads/账号库模板.xlsx
+++ b/src/uploads/账号库模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/hfpp2012/codes/task-backend/src/uploads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F356F30A-D206-F448-9A59-0E8580766722}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2F9F2CC-4F17-2945-AF8A-4BA27A896806}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8260" yWindow="3220" windowWidth="28040" windowHeight="17440" xr2:uid="{DA612C98-B207-AA43-B9D3-B2B5CC3324FF}"/>
   </bookViews>
